--- a/output/pdf_financials_xlsx/CRCL.xlsx
+++ b/output/pdf_financials_xlsx/CRCL.xlsx
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.024155</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>0</v>
@@ -3058,7 +3058,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.024155</v>
       </c>

--- a/output/pdf_financials_xlsx/CRCL.xlsx
+++ b/output/pdf_financials_xlsx/CRCL.xlsx
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.347221</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.241442</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.347221</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.241442</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/CRCL.xlsx
+++ b/output/pdf_financials_xlsx/CRCL.xlsx
@@ -985,10 +985,8 @@
       <c r="C34" s="3" t="n">
         <v>0.241442</v>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D34" s="3" t="n">
+        <v>0.578681</v>
       </c>
     </row>
     <row r="35">
@@ -1003,10 +1001,8 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1021,10 +1017,8 @@
       <c r="C36" s="3" t="n">
         <v>0.241442</v>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D36" s="3" t="n">
+        <v>0.578681</v>
       </c>
     </row>
     <row r="37">
@@ -1039,10 +1033,8 @@
       <c r="C37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1057,10 +1049,8 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1075,10 +1065,8 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1093,10 +1081,8 @@
       <c r="C40" s="3" t="n">
         <v>0.001871</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0.00287</v>
       </c>
     </row>
     <row r="41">
@@ -1111,10 +1097,8 @@
       <c r="C41" s="3" t="n">
         <v>0.001871</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D41" s="3" t="n">
+        <v>0.00287</v>
       </c>
     </row>
     <row r="42">
@@ -1129,10 +1113,8 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1147,10 +1129,8 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1165,10 +1145,8 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1183,10 +1161,8 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1201,10 +1177,8 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1219,10 +1193,8 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1237,10 +1209,8 @@
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1277,10 +1247,8 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1295,10 +1263,8 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1313,10 +1279,8 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1331,10 +1295,8 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1349,10 +1311,8 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1389,10 +1349,8 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1407,10 +1365,8 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1425,10 +1381,8 @@
       <c r="C58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1443,10 +1397,8 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1461,10 +1413,8 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1479,10 +1429,8 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1519,10 +1467,8 @@
       <c r="C63" s="3" t="n">
         <v>0.243313</v>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D63" s="3" t="n">
+        <v>0.592403</v>
       </c>
     </row>
     <row r="64">
@@ -1532,15 +1478,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.006637</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007019</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.035378</v>
       </c>
     </row>
     <row r="65">
@@ -1555,10 +1499,8 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1573,10 +1515,8 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1586,15 +1526,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.016561</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01749</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.06875000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -1609,10 +1547,8 @@
       <c r="C68" s="3" t="n">
         <v>0.024509</v>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D68" s="3" t="n">
+        <v>0.104128</v>
       </c>
     </row>
     <row r="69">
@@ -1627,10 +1563,8 @@
       <c r="C69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1645,10 +1579,8 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1663,10 +1595,8 @@
       <c r="C71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1681,10 +1611,8 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1699,10 +1627,8 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1717,10 +1643,8 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1735,10 +1659,8 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1775,10 +1697,8 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1793,10 +1713,8 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1811,10 +1729,8 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1851,10 +1767,8 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1869,10 +1783,8 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1887,10 +1799,8 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1905,10 +1815,8 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1923,10 +1831,8 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1963,10 +1869,8 @@
       <c r="C87" s="3" t="n">
         <v>0.024509</v>
       </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D87" s="3" t="n">
+        <v>0.104128</v>
       </c>
     </row>
     <row r="88">
@@ -1981,10 +1885,8 @@
       <c r="C88" s="3" t="n">
         <v>0.8978390000000001</v>
       </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D88" s="3" t="n">
+        <v>3.24862</v>
       </c>
     </row>
     <row r="89">
@@ -1999,10 +1901,8 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2017,10 +1917,8 @@
       <c r="C90" s="3" t="n">
         <v>-0.6790350000000001</v>
       </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D90" s="3" t="n">
+        <v>-3.822647</v>
       </c>
     </row>
     <row r="91">
@@ -2035,10 +1933,8 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2053,10 +1949,8 @@
       <c r="C92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D92" s="3" t="n">
+        <v>1.062302</v>
       </c>
     </row>
     <row r="93">
@@ -2071,10 +1965,8 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2089,10 +1981,8 @@
       <c r="C94" s="3" t="n">
         <v>0.218804</v>
       </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D94" s="3" t="n">
+        <v>0.488275</v>
       </c>
     </row>
     <row r="95">
@@ -2107,10 +1997,8 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2125,10 +2013,8 @@
       <c r="C96" s="3" t="n">
         <v>0.218804</v>
       </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D96" s="3" t="n">
+        <v>0.488275</v>
       </c>
     </row>
     <row r="97">
@@ -2143,10 +2029,8 @@
       <c r="C97" s="3" t="n">
         <v>0.8992696649994041</v>
       </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D97" s="3" t="n">
+        <v>0.8242277638702032</v>
       </c>
     </row>
     <row r="98">
@@ -2773,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2825,23 +2709,29 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>June 30, 2024 June</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E2" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.347221</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.241442</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.578681</v>
       </c>
     </row>
     <row r="3">
@@ -2857,24 +2747,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Other receivables (Note 4)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
+          <t>OtherReceivables</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.347221</v>
+        <v>0.001547</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.241442</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001871</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.00287</v>
       </c>
     </row>
     <row r="4">
@@ -2890,24 +2778,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other receivables (Note 4)</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherReceivables</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.001547</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.001871</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.010852</v>
       </c>
     </row>
     <row r="5">
@@ -2937,10 +2827,8 @@
       <c r="F5" s="5" t="n">
         <v>0.243313</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G5" s="5" t="n">
+        <v>0.592403</v>
       </c>
     </row>
     <row r="6">
@@ -2956,7 +2844,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 5 and 9)</t>
+          <t>Accounts payable and accrued liabilities (Notes 5, 11)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2964,16 +2852,16 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>0.023198</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.024509</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G6" s="5" t="n">
+        <v>0.104128</v>
       </c>
     </row>
     <row r="7">
@@ -3003,10 +2891,8 @@
       <c r="F7" s="5" t="n">
         <v>0.024509</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G7" s="5" t="n">
+        <v>0.104128</v>
       </c>
     </row>
     <row r="8">
@@ -3015,14 +2901,10 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Share capital (Note 6)</t>
+          <t>Share capital (Note 7)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3030,16 +2912,16 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>0.847839</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.8978390000000001</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" s="5" t="n">
+        <v>3.24862</v>
       </c>
     </row>
     <row r="9">
@@ -3048,14 +2930,10 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Warrants reserve (Note 8)</t>
+          <t>Contributed surplus (Note 8)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3063,18 +2941,18 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>0.024155</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G9" s="5" t="n">
+        <v>0.356502</v>
       </c>
     </row>
     <row r="10">
@@ -3083,31 +2961,29 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Reserve for warrants (Note 9)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>-0.546424</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-0.6790350000000001</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.7058</v>
       </c>
     </row>
     <row r="11">
@@ -3116,31 +2992,27 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.32557</v>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.218804</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.6790350000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.822647</v>
       </c>
     </row>
     <row r="12">
@@ -3149,119 +3021,109 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders’ Equity</t>
+          <t>Total Shareholders' Equity</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.348768</v>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.243313</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.218804</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.488275</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Operating Activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Total Liabilities and Shareholders' Equity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>-0.116118</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-0.156766</v>
+        <v>0.243313</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-3.143612</v>
+        <v>0.592403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Adjustments for non-cash items</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Interest expense (Note 6)</t>
+          <t>June 30, 2024 June</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.007376</v>
+      <c r="E14" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Shares issued for property extension (Notes 7 and 12)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities (Notes 5 and 9)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.023198</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.05</v>
+        <v>0.024509</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3272,162 +3134,168 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 8, 11)</t>
+          <t>Share capital (Note 6)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.356502</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.847839</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.8978390000000001</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses incurred on acquisition (Note</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1.996881</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>1.3e-05</v>
+          <t>Warrants reserve (Note 8)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.024155</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items total</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.546424</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.106766</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.782853</v>
+        <v>-0.6790350000000001</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other receivables (Note 4)</t>
+          <t>Total Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.32557</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.000323</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>-0.0009990000000000001</v>
+        <v>0.218804</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Total Liabilities and Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-0.008071999999999999</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.348768</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.243313</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -3438,29 +3306,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Notes 5, 11)</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-0.116118</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.00131</v>
+        <v>-0.156766</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.09342200000000001</v>
+        <v>-3.143612</v>
       </c>
     </row>
     <row r="22">
@@ -3471,29 +3337,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cash Flows used in Operating Activities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Interest expense (Note 6)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n">
-        <v>-0.105779</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.885346</v>
+        <v>0.007376</v>
       </c>
     </row>
     <row r="23">
@@ -3504,12 +3368,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Repayment of promissory notes (Note 6)</t>
+          <t>Shares issued for property extension (Notes 7 and 12)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -3518,13 +3382,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>-0.270574</v>
+      <c r="F23" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -3535,15 +3399,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net cash from acquisition (Note 13)</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Share-based payments (Note 8, 11)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -3555,7 +3423,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.086578</v>
+        <v>0.356502</v>
       </c>
     </row>
     <row r="25">
@@ -3566,31 +3434,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cash flows used in Investing Activities</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses incurred on acquisition (Note</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="5" t="n">
+        <v>1.996881</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.183996</v>
+        <v>1.3e-05</v>
       </c>
     </row>
     <row r="26">
@@ -3601,12 +3463,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Proceeds from private placements (Notes 7, 9)</t>
+          <t>Adjustments for non-cash items total</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3615,13 +3477,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>-0.106766</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.434</v>
+        <v>-0.782853</v>
       </c>
     </row>
     <row r="27">
@@ -3632,17 +3492,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Share issuance costs (Notes 7, 9)</t>
+          <t>Other receivables (Note 4)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3650,13 +3510,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="5" t="n">
+        <v>-0.000323</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.027419</v>
+        <v>-0.0009990000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3667,17 +3525,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash flows from Financing Activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3691,7 +3549,7 @@
         </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.406581</v>
+        <v>-0.008071999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3702,17 +3560,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
+          <t>Accounts payable and accrued liabilities (Notes 5, 11)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3721,10 +3579,10 @@
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.105779</v>
+        <v>0.00131</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.337239</v>
+        <v>-0.09342200000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3735,17 +3593,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Cash Flows used in Operating Activities</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3754,10 +3612,10 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.347221</v>
+        <v>-0.105779</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.241442</v>
+        <v>-0.885346</v>
       </c>
     </row>
     <row r="31">
@@ -3768,29 +3626,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Repayment of promissory notes (Note 6)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>0.241442</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.578681</v>
+        <v>-0.270574</v>
       </c>
     </row>
     <row r="32">
@@ -3801,25 +3657,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shares issued for property acquisition (Notes 8 and</t>
+          <t>Net cash from acquisition (Note 13)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.086578</v>
       </c>
     </row>
     <row r="33">
@@ -3830,29 +3688,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Other receivables</t>
+          <t>Cash flows used in Investing Activities</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0.003217</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>-0.000323</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.183996</v>
       </c>
     </row>
     <row r="34">
@@ -3863,29 +3723,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>-0.010679</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.00131</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from private placements (Notes 7, 9)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1.434</v>
       </c>
     </row>
     <row r="35">
@@ -3896,29 +3754,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash Flows (used in) Operating Activities</t>
+          <t>Share issuance costs (Notes 7, 9)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>-0.12358</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>-0.105779</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>-0.027419</v>
       </c>
     </row>
     <row r="36">
@@ -3929,29 +3789,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Decrease in cash</t>
+          <t>Cash flows from Financing Activities</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>-0.12358</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>-0.105779</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.406581</v>
       </c>
     </row>
     <row r="37">
@@ -3962,29 +3824,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.470801</v>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.347221</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.105779</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.337239</v>
       </c>
     </row>
     <row r="38">
@@ -3995,277 +3857,289 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>0.347221</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="G38" s="5" t="n">
         <v>0.241442</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (Note 12, 13)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.052027</v>
+        <v>0.241442</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.450827</v>
+        <v>0.578681</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11, 16)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for property acquisition (Notes 8 and</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>0.05</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.088585</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.307884</v>
+        <v>1e-05</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.002908</v>
+        <v>0.003217</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.009638000000000001</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.019631</v>
+        <v>-0.000323</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transfer agent fees</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.005678</v>
+        <v>-0.010679</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.006516</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.008768</v>
+        <v>0.00131</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 8, 11)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.356502</v>
+          <t>Cash Flows (used in) Operating Activities</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-0.12358</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-0.105779</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss</t>
+          <t>Decrease in cash</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>-0.116118</v>
+        <v>-0.12358</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.156766</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>-3.143612</v>
+        <v>-0.105779</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Ourstanding Shares</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>- Basic and diluted (Note 10)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.470801</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>22.632514</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>32.321616</v>
+        <v>0.347221</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Ourstanding Shares</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net Loss per Share - Basic and Diluted (Note 10)</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.347221</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>-7e-09</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-9.700000000000001e-08</v>
+        <v>0.241442</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -4276,12 +4150,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 21,750,000 847,839 - 24,155</t>
+          <t>Exploration and evaluation expenses (Note 12, 13)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4291,10 +4165,10 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.32557</v>
+        <v>0.052027</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.546424</v>
+        <v>2.450827</v>
       </c>
     </row>
     <row r="48">
@@ -4305,27 +4179,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Issuance of shares for Property Acquisition (Notes 7 and 12) 1,000,000 50,000 - -</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Professional fees (Note 11, 16)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.088585</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.307884</v>
       </c>
     </row>
     <row r="49">
@@ -4336,27 +4212,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Expiry of Warrants (Note 9) - - - (24,155)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.002908</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.009638000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.024155</v>
+        <v>0.019631</v>
       </c>
     </row>
     <row r="50">
@@ -4367,29 +4243,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss - - - -</t>
+          <t>Transfer agent fees</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.005678</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.156766</v>
+        <v>0.006516</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.156766</v>
+        <v>0.008768</v>
       </c>
     </row>
     <row r="51">
@@ -4400,12 +4274,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2024 22,750,000 897,839 - -</t>
+          <t>Share-based payments (Note 8, 11)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4414,11 +4288,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.218804</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.6790350000000001</v>
+        <v>0.356502</v>
       </c>
     </row>
     <row r="52">
@@ -4429,27 +4305,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shares issued on acquisition of CuQuest Resources Corp. (Notes 7 and 13) 15,000,000 1,650,000 - -</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net Loss and Comprehensive Loss</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>-0.116118</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.156766</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-3.143612</v>
       </c>
     </row>
     <row r="53">
@@ -4460,12 +4336,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted Average Number of Ourstanding Shares</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Proceeds from Private Placements (Notes 7 and 9) 9,560,000 729,549 - 704,451</t>
+          <t>- Basic and diluted (Note 10)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4475,12 +4351,10 @@
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>1.434</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>22.632514</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>32.321616</v>
       </c>
     </row>
     <row r="54">
@@ -4491,27 +4365,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted Average Number of Ourstanding Shares</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share issuance Costs (Notes 7 and 9) - (13,949) - (13,470)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Net Loss per Share - Basic and Diluted (Note 10)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.027419</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7e-09</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-9.700000000000001e-08</v>
       </c>
     </row>
     <row r="55">
@@ -4527,7 +4403,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Issuance of Finders' Warrants (Note 9) - (14,819) - 14,819</t>
+          <t>Balance, June 30, 2023 21,750,000 847,839 - 24,155</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4536,15 +4412,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F55" s="5" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.546424</v>
       </c>
     </row>
     <row r="56">
@@ -4560,7 +4432,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share-based Compensation (Note 8, 11) - - 356,502 -</t>
+          <t>Issuance of shares for Property Acquisition (Notes 7 and 12) 1,000,000 50,000 - -</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4570,7 +4442,7 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.356502</v>
+        <v>0.05</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4591,7 +4463,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2025 47,310,000 3,248,620 356,502 705,800</t>
+          <t>Expiry of Warrants (Note 9) - - - (24,155)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -4600,11 +4472,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.488275</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-3.822647</v>
+        <v>0.024155</v>
       </c>
     </row>
     <row r="58">
@@ -4615,29 +4489,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Professional fees (Notes 9 and 14)</t>
+          <t>Net Loss and Comprehensive Loss - - - -</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0.077448</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.088585</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.156766</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.156766</v>
       </c>
     </row>
     <row r="59">
@@ -4648,25 +4522,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 11)</t>
+          <t>Balance, June 30, 2024 22,750,000 897,839 - -</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
-        <v>0.030084</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.052027</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.218804</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.6790350000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4677,20 +4551,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>– Basic and diluted</t>
+          <t>Shares issued on acquisition of CuQuest Resources Corp. (Notes 7 and 13) 15,000,000 1,650,000 - -</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>21.75</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>22.632514</v>
+        <v>1.65</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4706,24 +4582,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Net Loss per Share – Basic and Diluted (Note 7)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>-5e-09</v>
+          <t>Proceeds from Private Placements (Notes 7 and 9) 9,560,000 729,549 - 704,451</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-7e-09</v>
+        <v>1.434</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4744,15 +4618,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2022 21,750,000 847,839 24,155</t>
+          <t>Share issuance Costs (Notes 7 and 9) - (13,949) - (13,470)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.441688</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.430306</v>
+        <v>-0.027419</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4773,19 +4649,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - -</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>-0.116118</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.116118</v>
+          <t>Issuance of Finders' Warrants (Note 9) - (14,819) - 14,819</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4806,15 +4682,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 21,750,000 847,839 24,155</t>
+          <t>Share-based Compensation (Note 8, 11) - - 356,502 -</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>0.32557</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.546424</v>
+        <v>0.356502</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4835,22 +4713,20 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Issuance of shares for property extension (Notes 6 and 10) 1,000,000 50,000 -</t>
+          <t>Balance, June 30, 2025 47,310,000 3,248,620 356,502 705,800</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.488275</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-3.822647</v>
       </c>
     </row>
     <row r="66">
@@ -4861,22 +4737,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Expiry of agent’s warrants (Note 8) - - (24,155)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees (Notes 9 and 14)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.077448</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.024155</v>
+        <v>0.088585</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4892,22 +4770,266 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2024 22,750,000 897,839 -</t>
+          <t>Exploration and evaluation expenditures (Note 11)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
+        <v>0.030084</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.052027</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Outstanding Shares</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>– Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>22.632514</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Outstanding Shares</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Net Loss per Share – Basic and Diluted (Note 7)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-5e-09</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-7e-09</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2022 21,750,000 847,839 24,155</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>0.441688</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-0.430306</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss - - -</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-0.116118</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.116118</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2023 21,750,000 847,839 24,155</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.546424</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Issuance of shares for property extension (Notes 6 and 10) 1,000,000 50,000 -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Expiry of agent’s warrants (Note 8) - - (24,155)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.024155</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Balance, June 30, 2024 22,750,000 897,839 -</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
         <v>0.218804</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F75" s="5" t="n">
         <v>-0.6790350000000001</v>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
